--- a/Input/lib_mois.xlsx
+++ b/Input/lib_mois.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="124519"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
   <si>
     <t>01</t>
   </si>
@@ -175,6 +175,15 @@
   </si>
   <si>
     <t>ar</t>
+  </si>
+  <si>
+    <t>prep_fr</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>d'</t>
   </si>
 </sst>
 </file>
@@ -491,7 +500,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -499,14 +508,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="4" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>48</v>
       </c>
@@ -519,8 +528,11 @@
       <c r="D1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,8 +545,11 @@
       <c r="D2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -547,8 +562,11 @@
       <c r="D3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -561,8 +579,11 @@
       <c r="D4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -575,8 +596,11 @@
       <c r="D5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -589,8 +613,11 @@
       <c r="D6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -603,8 +630,11 @@
       <c r="D7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -617,8 +647,11 @@
       <c r="D8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -631,8 +664,11 @@
       <c r="D9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -645,8 +681,11 @@
       <c r="D10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -659,8 +698,11 @@
       <c r="D11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -673,8 +715,11 @@
       <c r="D12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -686,6 +731,9 @@
       </c>
       <c r="D13" t="s">
         <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
